--- a/experiment/Omni_bestx4/Test/results-Set14/Set14.xlsx
+++ b/experiment/Omni_bestx4/Test/results-Set14/Set14.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23.02</v>
+        <v>23.04</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5326</v>
+        <v>0.5372</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>26.16</v>
+        <v>25.85</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7549</v>
+        <v>0.7524</v>
       </c>
     </row>
     <row r="4">
@@ -481,7 +481,7 @@
         <v>25.43</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6369</v>
+        <v>0.6389</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>26.35</v>
+        <v>26.23</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5783</v>
+        <v>0.5782</v>
       </c>
     </row>
     <row r="6">
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>23.59</v>
+        <v>23.62</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7347</v>
+        <v>0.7412</v>
       </c>
     </row>
     <row r="7">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32.9</v>
+        <v>32.86</v>
       </c>
       <c r="C7" t="n">
         <v>0.7946</v>
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>28.28</v>
+        <v>28.38</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8189</v>
+        <v>0.8231000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -543,10 +543,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>33.86</v>
+        <v>33.78</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9219000000000001</v>
+        <v>0.9203</v>
       </c>
     </row>
     <row r="10">
@@ -556,10 +556,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>32.48</v>
+        <v>32.43</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8642</v>
+        <v>0.8651</v>
       </c>
     </row>
     <row r="11">
@@ -572,7 +572,7 @@
         <v>27.39</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7502</v>
+        <v>0.7514</v>
       </c>
     </row>
     <row r="12">
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>32.9</v>
+        <v>33.03</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9445</v>
+        <v>0.9458</v>
       </c>
     </row>
     <row r="13">
@@ -595,10 +595,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>34.25</v>
+        <v>34.32</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8796</v>
+        <v>0.8807</v>
       </c>
     </row>
     <row r="14">
@@ -608,10 +608,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>26.54</v>
+        <v>26.63</v>
       </c>
       <c r="C14" t="n">
-        <v>0.946</v>
+        <v>0.949</v>
       </c>
     </row>
     <row r="15">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>27.4</v>
+        <v>27.38</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7779</v>
+        <v>0.7786999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -634,10 +634,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>28.61</v>
+        <v>28.6</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7811</v>
+        <v>0.7826</v>
       </c>
     </row>
   </sheetData>
